--- a/AAII_Financials/Quarterly/BKRIY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BKRIY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="92">
   <si>
     <t>BKRIY</t>
   </si>
@@ -656,74 +656,80 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="17" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="19" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -769,8 +775,14 @@
       <c r="Q8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -816,8 +828,14 @@
       <c r="Q9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -863,8 +881,14 @@
       <c r="Q10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -882,8 +906,10 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -929,8 +955,14 @@
       <c r="Q12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -976,8 +1008,14 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1023,8 +1061,14 @@
       <c r="Q14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1070,8 +1114,14 @@
       <c r="Q15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1086,8 +1136,10 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1133,8 +1185,14 @@
       <c r="Q17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1180,8 +1238,14 @@
       <c r="Q18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1199,8 +1263,10 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1246,8 +1312,14 @@
       <c r="Q20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1293,8 +1365,14 @@
       <c r="Q21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1340,8 +1418,14 @@
       <c r="Q22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1387,8 +1471,14 @@
       <c r="Q23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1434,8 +1524,14 @@
       <c r="Q24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1481,8 +1577,14 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1528,8 +1630,14 @@
       <c r="Q26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1575,8 +1683,14 @@
       <c r="Q27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1622,8 +1736,14 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1669,8 +1789,14 @@
       <c r="Q29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1716,8 +1842,14 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1763,8 +1895,14 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1810,8 +1948,14 @@
       <c r="Q32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1857,8 +2001,14 @@
       <c r="Q33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1904,8 +2054,14 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1951,60 +2107,72 @@
       <c r="Q35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2022,8 +2190,10 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2041,149 +2211,169 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>22154700</v>
+      </c>
+      <c r="E41" s="3">
+        <v>22359000</v>
+      </c>
+      <c r="F41" s="3">
         <v>25046400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>25028700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>29736900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>27368100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>32615200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>35136100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>33369800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>33600200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>34803800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>33326600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>37172500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>36994800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>38634200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>35448100</v>
       </c>
     </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>2969300</v>
+      </c>
+      <c r="E42" s="3">
+        <v>2996700</v>
+      </c>
+      <c r="F42" s="3">
         <v>4049500</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>4046700</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>4323000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>3978600</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>4243700</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>4571700</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>3798300</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>3824600</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>5129900</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>4912200</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>4714000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>4691400</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>5274100</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="S42" s="3">
         <v>4839200</v>
       </c>
     </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>251300</v>
+      </c>
+      <c r="E43" s="3">
+        <v>253700</v>
+      </c>
+      <c r="F43" s="3">
         <v>1475900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>1474800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>195000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>179400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>1049800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>1130900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>159600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>160800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>1078800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>1033000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>194300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>193400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>759900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>697200</v>
       </c>
     </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2229,243 +2419,279 @@
       <c r="Q44" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S44" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F45" s="3">
         <v>500200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>499800</v>
       </c>
-      <c r="F45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H45" s="3">
+      <c r="H45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J45" s="3">
         <v>299200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>322300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>33200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>33400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>334900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>320700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>1100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>1100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>288600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>264800</v>
       </c>
     </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>26517800</v>
+      </c>
+      <c r="E46" s="3">
+        <v>26762400</v>
+      </c>
+      <c r="F46" s="3">
         <v>34395900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>34371700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>36603600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>33687900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>40597400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>43735200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>38432400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>38697800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>43434300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>41590800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>42552400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>42349000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>48355200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>44367500</v>
       </c>
     </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>59880000</v>
+      </c>
+      <c r="E47" s="3">
+        <v>60432400</v>
+      </c>
+      <c r="F47" s="3">
         <v>55413900</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>55374900</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>46959500</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>43218800</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>35183800</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>37903200</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>34678000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>34917500</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>34010200</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>32566700</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>32123400</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>31969800</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>29329900</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>26911200</v>
       </c>
     </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>931100</v>
+      </c>
+      <c r="E48" s="3">
+        <v>939700</v>
+      </c>
+      <c r="F48" s="3">
         <v>925200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>924600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>948900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>873300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>823100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>886700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>871100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>877100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>876500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>839300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>907200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>902900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>843200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>773700</v>
       </c>
     </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1827900</v>
+      </c>
+      <c r="E49" s="3">
+        <v>1844800</v>
+      </c>
+      <c r="F49" s="3">
         <v>1871600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>1870200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>1843800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>1696900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>1553000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>1673000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>1599700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>1610700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>1556300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>1490300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>1473800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>1466800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>1363700</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>1251200</v>
       </c>
     </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2511,8 +2737,14 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2558,55 +2790,67 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>5267900</v>
+      </c>
+      <c r="E52" s="3">
+        <v>5316500</v>
+      </c>
+      <c r="F52" s="3">
         <v>3590500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>3587900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>5093400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>4687600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>3351300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>3610300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>4541900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>4573300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>3212100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>3075800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>4415900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>4394800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>3189100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>2926100</v>
       </c>
     </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2652,55 +2896,67 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>192614000</v>
+      </c>
+      <c r="E54" s="3">
+        <v>194390600</v>
+      </c>
+      <c r="F54" s="3">
         <v>193494200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>193358000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>190694100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>175503700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>167525600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>180474000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>170506800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>171684100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>172110100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>164805200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>170541500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>169726200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>161044100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>147763300</v>
       </c>
     </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2718,8 +2974,10 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2737,290 +2995,328 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>124470500</v>
+      </c>
+      <c r="E57" s="3">
+        <v>125618600</v>
+      </c>
+      <c r="F57" s="3">
         <v>127225500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>127136000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>124219600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>114324500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>108176800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>116538000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>110579700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>111343200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>113715000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>108888700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>114325300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>113778800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>109057400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>100063700</v>
       </c>
     </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1821100</v>
+      </c>
+      <c r="E58" s="3">
+        <v>1837900</v>
+      </c>
+      <c r="F58" s="3">
         <v>2275400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>2273800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>3694700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>3400300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>4350300</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>4686600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>3194000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>3216100</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>3791300</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>3630400</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>3931200</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>3912400</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>4989800</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>4578300</v>
       </c>
     </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1180200</v>
+      </c>
+      <c r="E59" s="3">
+        <v>1191100</v>
+      </c>
+      <c r="F59" s="3">
         <v>1702500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>1701300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>1193200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>1098100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>770300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>829800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>849700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>855500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>989300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>947300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>1301300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>1295100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>955400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>876600</v>
       </c>
     </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>127471700</v>
+      </c>
+      <c r="E60" s="3">
+        <v>128647500</v>
+      </c>
+      <c r="F60" s="3">
         <v>132127500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>132034500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>129107500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>118823000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>114103900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>122923300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>114623400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>115414800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>119358900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>114293000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>119557900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>118986300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>115548800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>106019800</v>
       </c>
     </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>12147800</v>
+      </c>
+      <c r="E61" s="3">
+        <v>12259900</v>
+      </c>
+      <c r="F61" s="3">
         <v>11647300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>11639100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>11923700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>10973800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>10915200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>11758900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>12890800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>12979800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>11737600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>11239400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>11411600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>11357000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>9496600</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>8713500</v>
       </c>
     </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>38037200</v>
+      </c>
+      <c r="E62" s="3">
+        <v>38388100</v>
+      </c>
+      <c r="F62" s="3">
         <v>34496900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>34472600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>34257200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>31528300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>28975000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>31214600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>29415000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>29618100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>27051000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>25902800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>26272900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>26147300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>23605900</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>21659100</v>
       </c>
     </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3066,8 +3362,14 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3113,8 +3415,14 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3160,55 +3468,67 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>177739100</v>
+      </c>
+      <c r="E66" s="3">
+        <v>179378500</v>
+      </c>
+      <c r="F66" s="3">
         <v>178324500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>178199000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>175347000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>161379200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>154057400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>165964800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>156996700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>158080700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>158225900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>151510400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>157306800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>156554800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>148730400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>136465000</v>
       </c>
     </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3226,8 +3546,10 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3273,8 +3595,14 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3320,8 +3648,14 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3367,8 +3701,14 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3414,55 +3754,67 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>12773900</v>
+      </c>
+      <c r="E72" s="3">
+        <v>12891700</v>
+      </c>
+      <c r="F72" s="3">
         <v>13035100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>13025900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>12835000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>11812600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>11553000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>12445900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>11651100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>11731600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>12023900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>11513500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>11336200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>11282100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>10427500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>9567600</v>
       </c>
     </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3508,8 +3860,14 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3555,8 +3913,14 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3602,55 +3966,67 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>14871500</v>
+      </c>
+      <c r="E76" s="3">
+        <v>15008600</v>
+      </c>
+      <c r="F76" s="3">
         <v>15166100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>15155500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>15343500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>14121300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>13465200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>14505900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>13506900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>13600200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>13880800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>13291700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>13161600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>13098700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>12242200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>11232600</v>
       </c>
     </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3696,60 +4072,72 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3795,8 +4183,14 @@
       <c r="Q81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3814,55 +4208,63 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>31100</v>
+      </c>
+      <c r="E83" s="3">
+        <v>28600</v>
+      </c>
+      <c r="F83" s="3">
         <v>-15000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>-16200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>31600</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>31800</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>-6100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>-5800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>28900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>28800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>-13900</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>-12700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>22500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>23900</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>-10800</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>-11000</v>
       </c>
     </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3908,8 +4310,14 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3955,8 +4363,14 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4002,8 +4416,14 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4049,8 +4469,14 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4096,55 +4522,67 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>473000</v>
+      </c>
+      <c r="E89" s="3">
+        <v>477300</v>
+      </c>
+      <c r="F89" s="3">
         <v>-229000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-228800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-230800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-212400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-105600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-113800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>1089100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>1096700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>886500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>848900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-3430100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-3413700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>499600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>458400</v>
       </c>
     </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4162,55 +4600,63 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-153700</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-155100</v>
+      </c>
+      <c r="F91" s="3">
         <v>66900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>66900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-160900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-148100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>57500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>61900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-134500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-135400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>51400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>49200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-114100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-113500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>24600</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>22600</v>
       </c>
     </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4256,8 +4702,14 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4303,55 +4755,67 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1812500</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-1829200</v>
+      </c>
+      <c r="F94" s="3">
         <v>-3618100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-3615500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-3691700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-3397600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-121600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-131100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-172500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-173700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-116600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-111700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-408800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-406900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>298700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>274100</v>
       </c>
     </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4369,55 +4833,63 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>266200</v>
+      </c>
+      <c r="E96" s="3">
+        <v>268600</v>
+      </c>
+      <c r="F96" s="3">
         <v>167900</v>
       </c>
-      <c r="E96" s="3">
+      <c r="G96" s="3">
         <v>167800</v>
       </c>
-      <c r="F96" s="3">
+      <c r="H96" s="3">
         <v>180900</v>
       </c>
-      <c r="G96" s="3">
+      <c r="I96" s="3">
         <v>166500</v>
       </c>
-      <c r="H96" s="3">
+      <c r="J96" s="3">
         <v>196700</v>
       </c>
-      <c r="I96" s="3">
+      <c r="K96" s="3">
         <v>211900</v>
       </c>
-      <c r="J96" s="3">
+      <c r="L96" s="3">
         <v>350900</v>
       </c>
-      <c r="K96" s="3">
+      <c r="M96" s="3">
         <v>353300</v>
       </c>
-      <c r="L96" s="3">
+      <c r="N96" s="3">
         <v>19300</v>
       </c>
-      <c r="M96" s="3">
+      <c r="O96" s="3">
         <v>18500</v>
       </c>
-      <c r="N96" s="3">
+      <c r="P96" s="3">
         <v>141400</v>
       </c>
-      <c r="O96" s="3">
+      <c r="Q96" s="3">
         <v>140700</v>
       </c>
-      <c r="P96" s="3">
+      <c r="R96" s="3">
         <v>19200</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="S96" s="3">
         <v>17700</v>
       </c>
     </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4463,8 +4935,14 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4510,8 +4988,14 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4557,145 +5041,169 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-159400</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-160800</v>
+      </c>
+      <c r="F100" s="3">
         <v>1172900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>1172100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>913700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>840900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>123700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>133300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-488600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-492000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-1251800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-1198700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>950900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>946300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-1683200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-1544400</v>
       </c>
     </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>45800</v>
+      </c>
+      <c r="E101" s="3">
+        <v>42200</v>
+      </c>
+      <c r="F101" s="3">
         <v>-15000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>-16200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>-19800</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>-20000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>17700</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>16900</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>-38200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>-38000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>50200</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>46100</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>39700</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>42200</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>-29600</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>-30100</v>
       </c>
     </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1443500</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-1456800</v>
+      </c>
+      <c r="F102" s="3">
         <v>-2647100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-2645200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-2963000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-2727000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-118500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-127700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>408200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>411000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-464200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-444500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-2926300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-2912300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-834700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-765800</v>
       </c>
     </row>
